--- a/GunfireDungeon_Godot/excel/WeaponBase@武器属性.xlsx
+++ b/GunfireDungeon_Godot/excel/WeaponBase@武器属性.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27360" windowHeight="14685"/>
+    <workbookView windowHeight="19560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -423,7 +423,7 @@
     <t>weapon0003</t>
   </si>
   <si>
-    <t>"Fire":["0003",null,null,null,null]</t>
+    <t>"Fire":["0003",null,null,null,null,null]</t>
   </si>
   <si>
     <t>[1]</t>
@@ -456,7 +456,7 @@
     <t>weapon0001</t>
   </si>
   <si>
-    <t>"Fire":["0001",null,null,null]</t>
+    <t>"Fire":["0001",null,null,null,null,null]</t>
   </si>
   <si>
     <t>reloadBegin0004</t>
@@ -480,7 +480,7 @@
     <t>weapon0002</t>
   </si>
   <si>
-    <t>"Fire":["0004",null,null,null]</t>
+    <t>"Fire":["0004",null,null,null,null,null,null,null]</t>
   </si>
   <si>
     <t>shell0002</t>
@@ -1629,58 +1629,58 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BH31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="21.225" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.2211538461538" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6833333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1083333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1083333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.225" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6826923076923" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1057692307692" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6634615384615" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1057692307692" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.2211538461538" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.225" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.2211538461538" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="54.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="14" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.775" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.0416666666667" style="1" customWidth="1"/>
-    <col min="16" max="16" width="23.225" style="1" customWidth="1"/>
-    <col min="17" max="17" width="33.475" style="1" customWidth="1"/>
-    <col min="18" max="18" width="34.275" style="1" customWidth="1"/>
-    <col min="19" max="19" width="23.6416666666667" style="1" customWidth="1"/>
-    <col min="20" max="20" width="27.6666666666667" style="1" customWidth="1"/>
-    <col min="21" max="22" width="25.075" style="1" customWidth="1"/>
-    <col min="23" max="23" width="25.225" style="1" customWidth="1"/>
-    <col min="24" max="24" width="23.6416666666667" style="1" customWidth="1"/>
-    <col min="25" max="25" width="24.8916666666667" style="1" customWidth="1"/>
-    <col min="26" max="26" width="21.3333333333333" style="1" customWidth="1"/>
-    <col min="27" max="27" width="23.3333333333333" style="1" customWidth="1"/>
-    <col min="28" max="28" width="20.9583333333333" style="1" customWidth="1"/>
-    <col min="29" max="29" width="23.1083333333333" style="1" customWidth="1"/>
-    <col min="30" max="31" width="23.775" style="1" customWidth="1"/>
-    <col min="32" max="32" width="20.475" style="1" customWidth="1"/>
-    <col min="33" max="33" width="26.65" style="1" customWidth="1"/>
-    <col min="34" max="34" width="26.5083333333333" style="1" customWidth="1"/>
-    <col min="35" max="35" width="29.2" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.9038461538462" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7788461538462" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.0384615384615" style="1" customWidth="1"/>
+    <col min="16" max="16" width="23.2211538461538" style="1" customWidth="1"/>
+    <col min="17" max="17" width="33.4711538461538" style="1" customWidth="1"/>
+    <col min="18" max="18" width="34.2788461538462" style="1" customWidth="1"/>
+    <col min="19" max="19" width="23.6442307692308" style="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6634615384615" style="1" customWidth="1"/>
+    <col min="21" max="22" width="25.0769230769231" style="1" customWidth="1"/>
+    <col min="23" max="23" width="25.2211538461538" style="1" customWidth="1"/>
+    <col min="24" max="24" width="23.6442307692308" style="1" customWidth="1"/>
+    <col min="25" max="25" width="24.8942307692308" style="1" customWidth="1"/>
+    <col min="26" max="26" width="21.3365384615385" style="1" customWidth="1"/>
+    <col min="27" max="27" width="23.3365384615385" style="1" customWidth="1"/>
+    <col min="28" max="28" width="20.9615384615385" style="1" customWidth="1"/>
+    <col min="29" max="29" width="23.1057692307692" style="1" customWidth="1"/>
+    <col min="30" max="31" width="23.7788461538462" style="1" customWidth="1"/>
+    <col min="32" max="32" width="20.4711538461538" style="1" customWidth="1"/>
+    <col min="33" max="33" width="26.6538461538462" style="1" customWidth="1"/>
+    <col min="34" max="34" width="26.5096153846154" style="1" customWidth="1"/>
+    <col min="35" max="35" width="29.2019230769231" style="1" customWidth="1"/>
     <col min="36" max="36" width="30" style="1" customWidth="1"/>
-    <col min="37" max="37" width="34.4" style="1" customWidth="1"/>
-    <col min="38" max="38" width="30.9833333333333" style="1" customWidth="1"/>
-    <col min="39" max="39" width="23.7" style="1" customWidth="1"/>
-    <col min="40" max="40" width="27.6416666666667" style="1" customWidth="1"/>
-    <col min="41" max="44" width="27.775" style="1" customWidth="1"/>
-    <col min="45" max="47" width="24.075" style="1" customWidth="1"/>
-    <col min="48" max="48" width="22.1" style="1" customWidth="1"/>
-    <col min="49" max="49" width="29.7583333333333" style="1" customWidth="1"/>
-    <col min="50" max="50" width="20.1166666666667" style="1" customWidth="1"/>
-    <col min="51" max="51" width="25.225" style="1" customWidth="1"/>
-    <col min="52" max="52" width="23.7" style="1" customWidth="1"/>
-    <col min="53" max="53" width="37.925" style="1" customWidth="1"/>
-    <col min="54" max="54" width="22.6" style="1" customWidth="1"/>
-    <col min="55" max="55" width="30.475" style="1" customWidth="1"/>
-    <col min="56" max="56" width="31.8583333333333" style="1" customWidth="1"/>
-    <col min="57" max="57" width="32.475" style="2" customWidth="1"/>
+    <col min="37" max="37" width="34.4038461538462" style="1" customWidth="1"/>
+    <col min="38" max="38" width="30.9807692307692" style="1" customWidth="1"/>
+    <col min="39" max="39" width="23.7019230769231" style="1" customWidth="1"/>
+    <col min="40" max="40" width="27.6442307692308" style="1" customWidth="1"/>
+    <col min="41" max="44" width="27.7788461538462" style="1" customWidth="1"/>
+    <col min="45" max="47" width="24.0769230769231" style="1" customWidth="1"/>
+    <col min="48" max="48" width="22.0961538461538" style="1" customWidth="1"/>
+    <col min="49" max="49" width="29.7596153846154" style="1" customWidth="1"/>
+    <col min="50" max="50" width="20.1153846153846" style="1" customWidth="1"/>
+    <col min="51" max="51" width="25.2211538461538" style="1" customWidth="1"/>
+    <col min="52" max="52" width="23.7019230769231" style="1" customWidth="1"/>
+    <col min="53" max="53" width="37.9230769230769" style="1" customWidth="1"/>
+    <col min="54" max="54" width="22.5961538461538" style="1" customWidth="1"/>
+    <col min="55" max="55" width="30.4711538461538" style="1" customWidth="1"/>
+    <col min="56" max="56" width="31.8557692307692" style="1" customWidth="1"/>
+    <col min="57" max="57" width="32.4711538461538" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="31" customHeight="1" spans="1:57">
@@ -6181,7 +6181,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -6193,7 +6193,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/GunfireDungeon_Godot/excel/WeaponBase@武器属性.xlsx
+++ b/GunfireDungeon_Godot/excel/WeaponBase@武器属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="19560"/>
+    <workbookView windowHeight="19180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     <t>CanMeleeAttack</t>
   </si>
   <si>
-    <t>MeleeAttackHarmRange</t>
+    <t>MeleeAttackDamageRange</t>
   </si>
   <si>
     <t>MeleeAttackRepelRange</t>
@@ -1670,7 +1670,9 @@
     <col min="39" max="39" width="23.7019230769231" style="1" customWidth="1"/>
     <col min="40" max="40" width="27.6442307692308" style="1" customWidth="1"/>
     <col min="41" max="44" width="27.7788461538462" style="1" customWidth="1"/>
-    <col min="45" max="47" width="24.0769230769231" style="1" customWidth="1"/>
+    <col min="45" max="45" width="24.0769230769231" style="1" customWidth="1"/>
+    <col min="46" max="46" width="27.25" style="1" customWidth="1"/>
+    <col min="47" max="47" width="24.0769230769231" style="1" customWidth="1"/>
     <col min="48" max="48" width="22.0961538461538" style="1" customWidth="1"/>
     <col min="49" max="49" width="29.7596153846154" style="1" customWidth="1"/>
     <col min="50" max="50" width="20.1153846153846" style="1" customWidth="1"/>
